--- a/data.xlsx
+++ b/data.xlsx
@@ -617,7 +617,7 @@
         <v>17</v>
       </c>
       <c r="E6" s="3">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>16</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -617,7 +617,7 @@
         <v>17</v>
       </c>
       <c r="E6" s="3">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>16</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,20 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomislav\Desktop\forestFriends\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A21A43F-C773-46AD-A700-DC1423F57471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="contact" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="products" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="services" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="about" sheetId="4" r:id="rId7"/>
+    <sheet name="contact" sheetId="1" r:id="rId1"/>
+    <sheet name="products" sheetId="2" r:id="rId2"/>
+    <sheet name="services" sheetId="3" r:id="rId3"/>
+    <sheet name="about" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
   <si>
     <t>number</t>
   </si>
@@ -31,9 +51,6 @@
     <t>map iframe</t>
   </si>
   <si>
-    <t>xxxx@gmail.com</t>
-  </si>
-  <si>
     <t>Pakrani 2, 43500, Pakrani</t>
   </si>
   <si>
@@ -61,21 +78,6 @@
     <t>image dir</t>
   </si>
   <si>
-    <t>Kesten</t>
-  </si>
-  <si>
-    <t>chestnut</t>
-  </si>
-  <si>
-    <t>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Pellentesque lacinia justo sit amet ullamcorper pretium. Vestibulum at dapibus mauris. Interdum et malesuada fames ac ante ipsum primis in faucibus.</t>
-  </si>
-  <si>
-    <t>Hrast</t>
-  </si>
-  <si>
-    <t>oak</t>
-  </si>
-  <si>
     <t>image</t>
   </si>
   <si>
@@ -85,105 +87,331 @@
     <t>Planting</t>
   </si>
   <si>
-    <t>Sadnja svih vrsta sadnica, s nasim ili vasim sadnicama.</t>
-  </si>
-  <si>
-    <t>Planting all types of seedlings, with our or your seedlings.</t>
-  </si>
-  <si>
-    <t>service1.png</t>
-  </si>
-  <si>
-    <t>Malčiranje</t>
-  </si>
-  <si>
-    <t>Mulching</t>
-  </si>
-  <si>
-    <t>Malčiranje svih vrsta terena.</t>
-  </si>
-  <si>
-    <t>Mulching all types of terrain.</t>
-  </si>
-  <si>
-    <t>service2.png</t>
-  </si>
-  <si>
-    <t>Košnja</t>
-  </si>
-  <si>
-    <t>Mowing</t>
-  </si>
-  <si>
-    <t>Košnja livada i travnjaka.</t>
-  </si>
-  <si>
-    <t>Mowing meadows and lawns.</t>
-  </si>
-  <si>
-    <t>service3.png</t>
-  </si>
-  <si>
     <t>title</t>
   </si>
   <si>
-    <t>Sadimo</t>
-  </si>
-  <si>
-    <t>We plant</t>
-  </si>
-  <si>
-    <t>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Maecenas interdum tellus facilisis, consectetur arcu molestie, posuere nibh. Aliquam pretium ante at libero ultrices congue. Nulla vitae volutpat nisl. Donec consequat risus eget dictum ornare. Etiam hendrerit ipsum lectus, ut venenatis purus placerat dignissim. Sed ut quam in purus tempor aliquet. Integer egestas, augue at tincidunt dignissim, sem libero tristique libero, at tincidunt nulla tortor et mauris. Nullam porttitor eu eros non consectetur. Maecenas et condimentum urna. Vestibulum malesuada accumsan ipsum, sit amet consequat mauris vehicula non. Curabitur ut blandit est. Suspendisse potenti.</t>
-  </si>
-  <si>
-    <t>plant.png</t>
-  </si>
-  <si>
-    <t>Kopamo</t>
-  </si>
-  <si>
-    <t>We bathe</t>
-  </si>
-  <si>
-    <t>bathe.jpg</t>
-  </si>
-  <si>
-    <t>Cistimo</t>
-  </si>
-  <si>
-    <t>We clean</t>
-  </si>
-  <si>
-    <t>clean.jpg</t>
+    <t>rasadnikbernat@gmail.com</t>
+  </si>
+  <si>
+    <t>Kesten pitomi kontejnerske sadnice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweet chestnut (Castanea sativa), bare root </t>
+  </si>
+  <si>
+    <t>Kesten pitomi, golog korjena</t>
+  </si>
+  <si>
+    <t>Sweet chestnut (Castanea sativa), container seedlings</t>
+  </si>
+  <si>
+    <t>Crvenolisni hrast, golog korjena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Oak ( Quercus rubra), bare root </t>
+  </si>
+  <si>
+    <t>Crvenolisni hrast, kontejnerske sadnice</t>
+  </si>
+  <si>
+    <t>Red Oak ( Quercus rubra), container seedlings</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Jednogodišnje sadnice pitomog kestena. Visina sadnica od 20-40cm
+- Dvogodišnje sadnice pitomog kestena. Visina sadnica 60-80cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
+- Plod: jestiv
+- Rodnost: obilna, redovita
+- Vrijeme dozrijevanja: listopad (1.-10.)
+- Oplodnja: potreban oprašivač
+- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Jednogodišnje sadnice pitomog kestena. Visina sadnica od 30-50cm
+- Kontejnerske sadnice
+- Sadnja moguća tijekom cijele godine
+Opis vrste:
+- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
+- Plod: jestiv
+- Rodnost: obilna, redovita
+- Vrijeme dozrijevanja: listopad (1.-10.)
+- Oplodnja: potreban oprašivač
+- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Jednogodišnje sadnice crvenog hrasta. Visina sadnica od 30-50cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
+- Ne stvara alergene.
+- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
+- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Jednogodišnje sadnice crvenog hrasta. Visina sadnica od 30-50cm
+- Kontejnerske sadnice
+- Sadnja moguća tijekom cijele godine
+Opis vrste:
+- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
+- Ne stvara alergene.
+- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
+- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
+  </si>
+  <si>
+    <t>Hrast lužnjak</t>
+  </si>
+  <si>
+    <t>Hrast kitnjak</t>
+  </si>
+  <si>
+    <t>Pedunculate (Quercus robur)</t>
+  </si>
+  <si>
+    <t>Sessile oak (Quercus petraea)</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+U ponudi: 
+- jednogodišnje sadnice hrasta lužnjaka (Quercus robur). Visina sadnica od 30-50cm
+- Dvogodišnje sadnice. Visina 70-90cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Listopadno stablo iz porodice bukva (Fagaceae). Naraste 40-50 m visine, deblo je promjera do 3 metra. Korijenov sustav je dobro razvijen, dubok, u početku jakog glavnog korijena, kasnije se razvijaju bočne žile. Krošnja je široka, vrlo dobro razgranata, nepravilna, grane su jake i debele, vodoravno stršeće.  
+- Stanište: Odgovaraju mu duboka i plodna, vlažna tla bogata vapnencem.   Otporan je na sušu i visoke temperature, na vjetar i gradska onečišćenja. Teško uspijeva na plitkom i suhom zemljištu, na tlima kisele reakcije i osjetljiv je na kasne mrazeve.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+U ponudi: 
+- Jednogodišnje sadnice hrasta kitnjaka (Quercus petraea). Visina sadnica od 30-50cm
+- Dvogodišnje sadnice. Visina 70-90cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste: 
+- Listopadno stablo iz porodice bukva (Fagaceae). Stablo naraste do 40 metara visine tvoreći bogato razgranatu, gustu i pravilnu krošnju. Korijenov sustav je dobro razvijen, s jakim središnjim korijenom. Deblo je promjera do 3 metra.
+- Stanište: Raste u brdskoplaninskim područjima, često zajedno uz obični grab, pitomi kesten ili bukvu. Raste od nizina do 1300 m nadmorske visine. Razmnožava se sjemenom koje brzo klija. Skromnih je zahtjeva prema staništu, odgovaraju mu svježa zemljišta, slabije uspijeva na tlu kisele reakcije.</t>
+  </si>
+  <si>
+    <t>Na upit</t>
+  </si>
+  <si>
+    <t>Seedling information:
+- One-year-old sweet chestnut seedlings. Seedling height 20-40cm
+- Two-year-old sweet chestnut seedlings. Seedling height 60-80cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+Species description:
+- Cultivation form: tree, with a lush, large crown.
+- Fruit: edible
+- Yield: abundant, regular
+- Ripening time: October (1-10)
+- Fertilization: pollinator required
+- Soil requirements: pH value from 4.5 to 6.0, must be moderately moist, loose, loamy-sandy texture. Best warm, sunny places, southern, southeastern and eastern exposures</t>
+  </si>
+  <si>
+    <t>Seedling information:
+- One-year-old sweet chestnut seedlings. Seedling height 30-50cm
+- Container seedlings
+- Planting possible throughout the year
+Species description:
+- Cultivation form: tree, with a lush, large crown.
+- Fruit: edible
+- Yield: abundant, regular
+- Ripening time: October (1-10)
+- Fertilization: pollinator required
+- Soil requirements: pH value from 4.5 to 6.0, must be moderately moist, loose, loamy-sandy texture. Best warm, sunny places, southern, southeastern and eastern exposures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+660
+'Seedling information:
+- One-year-old red oak seedlings. Seedling height 30-50cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+Species description:
+- Cultivation form: ornamental tree, with a lush, large crown.
+- Does not produce allergens.
+- Attractive deciduous tree known for its rapid growth and beautiful red color of leaves in autumn.
+- Habitat: The tree is resistant to low temperatures and urban pollution. It is relatively fast-growing, tolerates shade, tolerates most soils, thrives on poor and acidic soils, and is suitable for sandy and fresh soil. It does not tolerate flooded or dry habitats.</t>
+  </si>
+  <si>
+    <t>Seedling information:
+- One-year-old red oak seedlings. Seedling height 30-50cm
+- Container seedlings
+- Planting possible throughout the year
+Species description:
+- Cultivation form: ornamental tree, with a lush, large crown.
+- Does not produce allergens.
+- Attractive deciduous tree known for its rapid growth and beautiful red color of leaves in autumn.
+- Habitat: The tree is resistant to low temperatures and urban pollution. It is relatively fast-growing, tolerates shade, tolerates most soils, thrives on poor soils and acidic soils, and sandy and fresh soil is suitable for it. It does not tolerate flooded or dry habitats.</t>
+  </si>
+  <si>
+    <t>Seedling information:
+On offer:
+- one-year-old pedunculate oak seedlings (Quercus robur). Seedling height 30-50cm
+- two-year-old seedlings. Height 70-90cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+Species description:
+- Deciduous tree from the beech family (Fagaceae). It grows 40-50 m tall, the trunk is up to 3 meters in diameter. The root system is well developed, deep, initially with a strong main root, later lateral veins develop. The crown is wide, very well branched, irregular, the branches are strong and thick, horizontally protruding.
+- Habitat: It is suitable for deep and fertile, moist soils rich in limestone. It is resistant to drought and high temperatures, wind and urban pollution. It has difficulty growing in shallow and dry soil, on acidic soils, and is sensitive to late frosts.</t>
+  </si>
+  <si>
+    <t>Seedling information:
+On offer:
+- One-year-old sessile oak seedlings (Quercus petraea). Seedling height 30-50cm
+- Two-year-old seedlings. Height 70-90cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+Species description:
+- Deciduous tree from the beech family (Fagaceae). The tree grows up to 40 meters tall, forming a richly branched, dense and regular crown. The root system is well developed, with a strong central root. The trunk is up to 3 meters in diameter.
+- Habitat: It grows in hilly and mountainous areas, often together with common hornbeam, sweet chestnut or beech. It grows from lowlands to 1300 m above sea level. It reproduces by seeds that germinate quickly. It has modest requirements for habitat, it is suitable for fresh soils, it does not thrive well on acidic soils.</t>
+  </si>
+  <si>
+    <t>Vršimo uslugu konverzije vaše zapuštene poljoprivredne parcele iz degradiranog, zaraslog zemljišta u šumu. 
+Djelujemo na području kontinentalne Hrvatske.
+Uslugu radimo po principu "ključ u ruke". 
+Usluga podrazumijeva:
+- snimanje postojećeg stanja predmetne parcele.
+- izrada elaborata s opisom postojećeg stanja i smjernicama gospodarenja.
+- priprema i čišćenje parcele
+- sadnja dogovorenih biljnih vrsta
+- po dogovoru održavanje u narednim periodima
+Ako imate parcelu koja vam stoji zapuštena i nije privedena poljoprivrednoj proizvodnji a želite ostaviti nešto svojim budućim naraštajima, šuma je pravi odabir za vas.
+Zašto šuma? Zato što je prema našem mišljenju šuma nešto najvrijednije što možemo ostaviti našim budućim generacijama.
+Šuma se smatra savršenom ekološkom tvornicom, idealnim staništem za brojni životinjski svijet. 
+Šuma doprinosi očuvanju biološke raznolikosti, pročišćava zrak, proizvodi kisik, skladišti ugljikov dioksid. Šume štite zemljište od erozije, bujica i poplava.</t>
+  </si>
+  <si>
+    <t>Tko smo mi?</t>
+  </si>
+  <si>
+    <t>Stvaramo svijet u kojem su priroda i ljudi u harmoniji, osiguravajući održivu budućnost za sve generacije. Kroz aktivnu borbu protiv klimatskih promjena, obnavljanje ekosistema i odgovorno upravljanje prirodnim resursima, težimo očuvanju zdravih i prosperitetnih zajednica.</t>
+  </si>
+  <si>
+    <t>Naša misija je potaknuti zajednicu na očuvanje prirode putem sadnje i pošumljavanja, promičući svijest o važnosti ekološke ravnoteže. Angažiramo se u održivim praksama i obrazovnim inicijativama kako bismo osigurali da buduće generacije uživaju u istim prirodnim resursima i životnim uvjetima koji su dostupni nama danas, te jačamo lokalne zajednice u njihovoj borbi protiv klimatskih promjena.</t>
+  </si>
+  <si>
+    <t>Naša vizija</t>
+  </si>
+  <si>
+    <t>Naša misija</t>
+  </si>
+  <si>
+    <t>Our vision</t>
+  </si>
+  <si>
+    <t>Our mission</t>
+  </si>
+  <si>
+    <t>Who are we?</t>
+  </si>
+  <si>
+    <t>Obitelj smo  koja se bavi pošumljavanjem i proizvodnjom sadnica. Promičemo održive prakse gospodarenja šumama i osiguravamo bolju budućnost za generacije koje dolaze.</t>
+  </si>
+  <si>
+    <t>We are a family engaged in reforestation and seedling production. We promote sustainable forest management practices and ensure a better future for generations to come.</t>
+  </si>
+  <si>
+    <t>We provide a service of converting your neglected agricultural plot from degraded, overgrown land into a forest.
+We operate in continental part Republic of Croatia.
+We provide the service on a "turnkey" basis.
+The service includes:
+- surveying the current state of the plot in question.
+- preparation of a study with a description of the current state and management guidelines.
+- preparation and cleaning of the plot
+- planting of agreed plant species
+- maintenance in the following periods by agreement
+If you have a plot that is neglected and not used for agricultural production and you want to leave something for your future generations, a forest is the right choice for you.
+Why a forest? Because in our opinion, a forest is the most valuable thing we can leave to our future generations.
+A forest is considered a perfect ecological factory, an ideal habitat for numerous animal species.
+A forest contributes to the preservation of biodiversity, purifies the air, produces oxygen, stores carbon dioxide. Forests protect the land from erosion, torrents and floods.</t>
+  </si>
+  <si>
+    <t>We create a world where nature and people are in harmony, ensuring a sustainable future for all generations. Through the active fight against climate change, restoration of ecosystems and responsible management of natural resources, we strive to preserve healthy and prosperous communities.</t>
+  </si>
+  <si>
+    <t>Our mission is to encourage the community to preserve nature through planting and reforestation, promoting awareness of the importance of ecological balance. We engage in sustainable practices and educational initiatives to ensure that future generations enjoy the same natural resources and living conditions available to us today, and strengthen local communities in their fight against climate change.</t>
+  </si>
+  <si>
+    <t>kesten_golog_korjena</t>
+  </si>
+  <si>
+    <t>kesten_kontejnerska_sadnica</t>
+  </si>
+  <si>
+    <t>crvenolisni_hrast_golog_korjena</t>
+  </si>
+  <si>
+    <t>crvenolisni_hrast_kontejnerska_sadnica</t>
+  </si>
+  <si>
+    <t>hrast_luznjak_golog_korjena</t>
+  </si>
+  <si>
+    <t>hrast_kitnjak_golog_korjena</t>
+  </si>
+  <si>
+    <t>+385 99 245 9299</t>
+  </si>
+  <si>
+    <t>tko_smo_mi_1.jpg</t>
+  </si>
+  <si>
+    <t>vizija.jpg</t>
+  </si>
+  <si>
+    <t>misija_1.jpg</t>
+  </si>
+  <si>
+    <t>usluga_sadnje 1.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -191,55 +419,75 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -429,24 +677,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.13"/>
-    <col customWidth="1" min="2" max="2" width="13.63"/>
-    <col customWidth="1" min="3" max="3" width="20.13"/>
-    <col customWidth="1" min="4" max="4" width="36.25"/>
-    <col customWidth="1" min="5" max="5" width="365.13"/>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
+    <col min="4" max="4" width="36.28515625" customWidth="1"/>
+    <col min="5" max="5" width="365.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -463,335 +714,351 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="str">
-        <f>TEXT("+385 XX XXX XXXX", "")</f>
-        <v>+385 XX XXX XXXX</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="D2"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{945C7BDB-1534-4B51-B215-D404F9ABFCAD}"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="6.13"/>
-    <col customWidth="1" min="2" max="2" width="7.25"/>
-    <col customWidth="1" min="3" max="3" width="10.75"/>
-    <col customWidth="1" min="4" max="4" width="15.88"/>
-    <col customWidth="1" min="5" max="5" width="5.38"/>
+    <col min="1" max="1" width="29.85546875" customWidth="1"/>
+    <col min="2" max="2" width="47.140625" customWidth="1"/>
+    <col min="3" max="4" width="170.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2">
+    </row>
+    <row r="2" spans="1:6" ht="194.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="E2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="186.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="E3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="166.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>24</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="176.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>26</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="153" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.63"/>
-    <col customWidth="1" min="2" max="2" width="7.63"/>
-    <col customWidth="1" min="3" max="3" width="41.88"/>
-    <col customWidth="1" min="4" max="4" width="43.38"/>
-    <col customWidth="1" min="5" max="5" width="21.88"/>
-    <col customWidth="1" min="6" max="30" width="9.25"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="55.7109375" style="12" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" customWidth="1"/>
+    <col min="6" max="30" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="363" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>35</v>
-      </c>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="3"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="66.42578125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="70.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>